--- a/Liste.xlsx
+++ b/Liste.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33c026b07bb50802/Feina/Pre dataappa^0Learning projects/Classes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordiordonezadellach/Desktop/Projectes/Classes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{65C8032D-54D4-1F46-B5BA-F6CDAC424826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65DDB201-5094-4245-B4EB-7C205714741E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2388E678-873D-E748-AA77-C5A051FA4437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="-20540" windowWidth="28040" windowHeight="15820" xr2:uid="{B5B86117-F7DA-9D45-88D5-7A78429F12FC}"/>
+    <workbookView xWindow="1840" yWindow="-20560" windowWidth="28040" windowHeight="15820" xr2:uid="{B5B86117-F7DA-9D45-88D5-7A78429F12FC}"/>
   </bookViews>
   <sheets>
     <sheet name="liste" sheetId="1" r:id="rId1"/>
     <sheet name="classes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">liste!$A$1:$K$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">liste!$A$1:$N$234</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="261">
   <si>
     <t>Elèves à affecter</t>
   </si>
@@ -805,6 +805,21 @@
   </si>
   <si>
     <t>J</t>
+  </si>
+  <si>
+    <t>tech</t>
+  </si>
+  <si>
+    <t>cat i</t>
+  </si>
+  <si>
+    <t>pap</t>
+  </si>
+  <si>
+    <t>Origine</t>
+  </si>
+  <si>
+    <t>1+H140</t>
   </si>
 </sst>
 </file>
@@ -1348,10 +1363,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -1669,10 +1680,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041A12D7-D1F2-5E4A-959D-815F4F1F9005}">
-  <dimension ref="A1:K234"/>
+  <dimension ref="A1:O234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1689,25 +1700,37 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1724,22 +1747,34 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1756,16 +1791,28 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="N3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1782,13 +1829,25 @@
         <v>0</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="J4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1805,13 +1864,25 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1828,22 +1899,34 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
         <v>21</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1860,16 +1943,28 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="N7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1886,13 +1981,25 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="O8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1909,13 +2016,25 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1932,13 +2051,25 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>3</v>
       </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1955,22 +2086,34 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
         <v>27</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
         <v>28</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O11" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1987,13 +2130,25 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2010,13 +2165,25 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>3</v>
       </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2033,22 +2200,34 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
         <v>31</v>
       </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
         <v>32</v>
       </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2065,22 +2244,34 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
         <v>35</v>
       </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
         <v>36</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O15" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2097,13 +2288,25 @@
         <v>0</v>
       </c>
       <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>3</v>
       </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2120,16 +2323,28 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="N17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2146,13 +2361,25 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2169,13 +2396,25 @@
         <v>0</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>3</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2192,13 +2431,25 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2215,25 +2466,37 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
         <v>40</v>
       </c>
-      <c r="I21" t="s">
+      <c r="L21" t="s">
         <v>41</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>42</v>
       </c>
-      <c r="K21" t="s">
+      <c r="N21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O21" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2250,13 +2513,25 @@
         <v>0</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>3</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2273,13 +2548,25 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -2296,16 +2583,28 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="K24" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="N24" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -2322,13 +2621,25 @@
         <v>0</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>3</v>
       </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -2345,22 +2656,34 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
         <v>22</v>
       </c>
-      <c r="I26" t="s">
+      <c r="L26" t="s">
         <v>46</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -2377,13 +2700,25 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="O27" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2400,16 +2735,28 @@
         <v>0</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>3</v>
       </c>
-      <c r="G28">
-        <v>2</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="N28" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O28" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2426,13 +2773,25 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="O29" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2449,13 +2808,25 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -2472,13 +2843,25 @@
         <v>0</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
         <v>3</v>
       </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -2495,13 +2878,25 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -2518,22 +2913,34 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
         <v>51</v>
       </c>
-      <c r="I33" t="s">
+      <c r="L33" t="s">
         <v>52</v>
       </c>
-      <c r="J33" t="s">
+      <c r="M33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O33" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2550,13 +2957,25 @@
         <v>0</v>
       </c>
       <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>3</v>
       </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -2573,13 +2992,25 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="O35" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -2596,13 +3027,25 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O36" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -2619,13 +3062,25 @@
         <v>0</v>
       </c>
       <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
         <v>3</v>
       </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -2642,16 +3097,28 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>2</v>
-      </c>
-      <c r="K38" t="s">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="N38" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -2668,13 +3135,25 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -2691,13 +3170,25 @@
         <v>0</v>
       </c>
       <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
         <v>3</v>
       </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="O40" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>36</v>
       </c>
@@ -2714,13 +3205,25 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>57</v>
       </c>
@@ -2737,16 +3240,28 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>2</v>
-      </c>
-      <c r="K42" t="s">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="N42" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -2763,13 +3278,25 @@
         <v>0</v>
       </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
         <v>3</v>
       </c>
-      <c r="G43">
+      <c r="J43">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O43" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -2786,22 +3313,34 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44" t="s">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="s">
         <v>59</v>
       </c>
-      <c r="I44" t="s">
+      <c r="L44" t="s">
         <v>60</v>
       </c>
-      <c r="J44" t="s">
+      <c r="M44" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O44" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -2818,25 +3357,37 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
         <v>62</v>
       </c>
-      <c r="I45" t="s">
+      <c r="L45" t="s">
         <v>63</v>
       </c>
-      <c r="J45" t="s">
+      <c r="M45" t="s">
         <v>64</v>
       </c>
-      <c r="K45" t="s">
+      <c r="N45" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -2853,13 +3404,25 @@
         <v>0</v>
       </c>
       <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>3</v>
       </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -2876,13 +3439,25 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="O47" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -2899,13 +3474,25 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="O48" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -2922,16 +3509,28 @@
         <v>0</v>
       </c>
       <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
         <v>3</v>
       </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="K49" t="s">
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="N49" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O49" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -2948,13 +3547,25 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O50" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -2971,13 +3582,25 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="O51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -2994,13 +3617,25 @@
         <v>0</v>
       </c>
       <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
         <v>3</v>
       </c>
-      <c r="G52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="O52" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -3017,13 +3652,25 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -3040,13 +3687,25 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -3063,13 +3722,25 @@
         <v>0</v>
       </c>
       <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
         <v>3</v>
       </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -3086,13 +3757,25 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -3109,22 +3792,34 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>2</v>
-      </c>
-      <c r="H57" t="s">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57" t="s">
         <v>72</v>
       </c>
-      <c r="I57" t="s">
+      <c r="L57" t="s">
         <v>73</v>
       </c>
-      <c r="J57" t="s">
+      <c r="M57" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O57" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3141,13 +3836,25 @@
         <v>0</v>
       </c>
       <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
         <v>3</v>
       </c>
-      <c r="G58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="O58" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -3164,16 +3871,28 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>2</v>
-      </c>
-      <c r="K59" t="s">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="N59" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O59" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -3190,22 +3909,34 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
-      </c>
-      <c r="H60" t="s">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
         <v>78</v>
       </c>
-      <c r="I60" t="s">
+      <c r="L60" t="s">
         <v>79</v>
       </c>
-      <c r="J60" t="s">
+      <c r="M60" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O60" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -3222,13 +3953,25 @@
         <v>0</v>
       </c>
       <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
         <v>3</v>
       </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -3245,13 +3988,25 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="O62" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -3268,16 +4023,28 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>2</v>
-      </c>
-      <c r="K63" t="s">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="N63" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O63" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -3294,13 +4061,25 @@
         <v>0</v>
       </c>
       <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
         <v>3</v>
       </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -3317,13 +4096,25 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="O65" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>78</v>
       </c>
@@ -3340,13 +4131,25 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="O66" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -3363,13 +4166,25 @@
         <v>0</v>
       </c>
       <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
         <v>3</v>
       </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="O67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -3386,13 +4201,25 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="O68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>84</v>
       </c>
@@ -3409,16 +4236,28 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>2</v>
-      </c>
-      <c r="K69" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="N69" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O69" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>60</v>
       </c>
@@ -3435,13 +4274,25 @@
         <v>0</v>
       </c>
       <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
         <v>3</v>
       </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -3458,22 +4309,34 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
         <v>3</v>
       </c>
-      <c r="H71" t="s">
+      <c r="K71" t="s">
         <v>86</v>
       </c>
-      <c r="I71" t="s">
+      <c r="L71" t="s">
         <v>87</v>
       </c>
-      <c r="J71" t="s">
+      <c r="M71" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O71" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -3490,13 +4353,25 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O72" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -3513,16 +4388,28 @@
         <v>0</v>
       </c>
       <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
         <v>3</v>
       </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="K73" t="s">
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="N73" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O73" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -3539,13 +4426,25 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
         <v>3</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O74" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -3562,13 +4461,25 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="O75" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -3585,13 +4496,25 @@
         <v>0</v>
       </c>
       <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
         <v>3</v>
       </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -3608,13 +4531,25 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>2</v>
+      </c>
+      <c r="O77" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>91</v>
       </c>
@@ -3631,13 +4566,25 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -3654,13 +4601,25 @@
         <v>0</v>
       </c>
       <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
         <v>3</v>
       </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -3677,13 +4636,25 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="O80" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -3700,13 +4671,25 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -3723,13 +4706,25 @@
         <v>0</v>
       </c>
       <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
         <v>3</v>
       </c>
-      <c r="G82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="O82" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3746,16 +4741,28 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>1</v>
-      </c>
-      <c r="K83" t="s">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="N83" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O83" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -3772,22 +4779,34 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>1</v>
-      </c>
-      <c r="H84" t="s">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84" t="s">
         <v>99</v>
       </c>
-      <c r="I84" t="s">
+      <c r="L84" t="s">
         <v>100</v>
       </c>
-      <c r="J84" t="s">
+      <c r="M84" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O84" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -3804,13 +4823,25 @@
         <v>0</v>
       </c>
       <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
         <v>3</v>
       </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="O85" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3827,13 +4858,25 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="O86" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>103</v>
       </c>
@@ -3850,16 +4893,28 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="K87" t="s">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="N87" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O87" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -3876,13 +4931,25 @@
         <v>0</v>
       </c>
       <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
         <v>3</v>
       </c>
-      <c r="G88">
+      <c r="J88">
         <v>3</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O88" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>104</v>
       </c>
@@ -3899,13 +4966,25 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O89" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -3922,16 +5001,28 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>1</v>
-      </c>
-      <c r="K90" t="s">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>2</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="N90" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O90" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>106</v>
       </c>
@@ -3948,13 +5039,25 @@
         <v>0</v>
       </c>
       <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
         <v>3</v>
       </c>
-      <c r="G91">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="O91" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -3971,13 +5074,25 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>2</v>
+      </c>
+      <c r="O92" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -3994,13 +5109,25 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="O93" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -4017,16 +5144,28 @@
         <v>0</v>
       </c>
       <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
         <v>3</v>
       </c>
-      <c r="G94">
-        <v>2</v>
-      </c>
-      <c r="K94" t="s">
+      <c r="J94">
+        <v>2</v>
+      </c>
+      <c r="N94" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O94" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>105</v>
       </c>
@@ -4043,13 +5182,25 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -4066,13 +5217,25 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O96" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>87</v>
       </c>
@@ -4089,13 +5252,25 @@
         <v>0</v>
       </c>
       <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
         <v>3</v>
       </c>
-      <c r="G97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J97">
+        <v>2</v>
+      </c>
+      <c r="O97" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -4112,22 +5287,34 @@
         <v>0</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>2</v>
-      </c>
-      <c r="H98" t="s">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="K98" t="s">
         <v>112</v>
       </c>
-      <c r="I98" t="s">
+      <c r="L98" t="s">
         <v>113</v>
       </c>
-      <c r="J98" t="s">
+      <c r="M98" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O98" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -4144,13 +5331,25 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>2</v>
+      </c>
+      <c r="J99">
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>115</v>
       </c>
@@ -4167,13 +5366,25 @@
         <v>0</v>
       </c>
       <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
         <v>3</v>
       </c>
-      <c r="G100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="O100" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>116</v>
       </c>
@@ -4190,22 +5401,34 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101" t="s">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101" t="s">
         <v>117</v>
       </c>
-      <c r="I101" t="s">
+      <c r="L101" t="s">
         <v>118</v>
       </c>
-      <c r="J101" t="s">
+      <c r="M101" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O101" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>120</v>
       </c>
@@ -4222,13 +5445,25 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102">
+        <v>2</v>
+      </c>
+      <c r="O102" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>121</v>
       </c>
@@ -4245,13 +5480,25 @@
         <v>0</v>
       </c>
       <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
         <v>3</v>
       </c>
-      <c r="G103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="O103" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>112</v>
       </c>
@@ -4268,16 +5515,28 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104">
-        <v>1</v>
-      </c>
-      <c r="K104" t="s">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="N104" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O104" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -4294,13 +5553,25 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -4317,13 +5588,25 @@
         <v>0</v>
       </c>
       <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
         <v>3</v>
       </c>
-      <c r="G106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>117</v>
       </c>
@@ -4340,13 +5623,25 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>123</v>
       </c>
@@ -4363,16 +5658,28 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>2</v>
-      </c>
-      <c r="K108" t="s">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="N108" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O108" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>119</v>
       </c>
@@ -4389,13 +5696,25 @@
         <v>0</v>
       </c>
       <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
         <v>3</v>
       </c>
-      <c r="G109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>100</v>
       </c>
@@ -4412,13 +5731,25 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -4435,22 +5766,34 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>2</v>
-      </c>
-      <c r="H111" t="s">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
         <v>126</v>
       </c>
-      <c r="I111" t="s">
+      <c r="L111" t="s">
         <v>127</v>
       </c>
-      <c r="J111" t="s">
+      <c r="M111" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O111" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>129</v>
       </c>
@@ -4467,13 +5810,25 @@
         <v>0</v>
       </c>
       <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
         <v>3</v>
       </c>
-      <c r="G112">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>124</v>
       </c>
@@ -4490,13 +5845,25 @@
         <v>0</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>130</v>
       </c>
@@ -4513,13 +5880,25 @@
         <v>0</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>131</v>
       </c>
@@ -4536,16 +5915,28 @@
         <v>0</v>
       </c>
       <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
         <v>3</v>
       </c>
-      <c r="G115">
-        <v>2</v>
-      </c>
-      <c r="K115" t="s">
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="N115" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O115" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>133</v>
       </c>
@@ -4562,13 +5953,25 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>2</v>
+      </c>
+      <c r="O116" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -4585,13 +5988,25 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>2</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="O117" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -4608,13 +6023,25 @@
         <v>0</v>
       </c>
       <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
         <v>3</v>
       </c>
-      <c r="G118">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>128</v>
       </c>
@@ -4631,16 +6058,28 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>1</v>
-      </c>
-      <c r="K119" t="s">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="N119" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O119" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>132</v>
       </c>
@@ -4657,13 +6096,25 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
         <v>3</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O120" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -4680,13 +6131,25 @@
         <v>0</v>
       </c>
       <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
         <v>3</v>
       </c>
-      <c r="G121">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="O121" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -4703,22 +6166,34 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
         <v>3</v>
       </c>
-      <c r="H122" t="s">
+      <c r="K122" t="s">
         <v>137</v>
       </c>
-      <c r="I122" t="s">
+      <c r="L122" t="s">
         <v>138</v>
       </c>
-      <c r="J122" t="s">
+      <c r="M122" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O122" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>140</v>
       </c>
@@ -4735,22 +6210,34 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
         <v>3</v>
       </c>
-      <c r="H123" t="s">
+      <c r="K123" t="s">
         <v>141</v>
       </c>
-      <c r="I123" t="s">
+      <c r="L123" t="s">
         <v>142</v>
       </c>
-      <c r="J123" t="s">
+      <c r="M123" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O123" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>113</v>
       </c>
@@ -4767,13 +6254,25 @@
         <v>0</v>
       </c>
       <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
         <v>3</v>
       </c>
-      <c r="G124">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="O124" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>144</v>
       </c>
@@ -4790,13 +6289,25 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>145</v>
       </c>
@@ -4813,13 +6324,25 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>118</v>
       </c>
@@ -4836,13 +6359,25 @@
         <v>0</v>
       </c>
       <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
         <v>3</v>
       </c>
-      <c r="G127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J127">
+        <v>2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>137</v>
       </c>
@@ -4859,13 +6394,25 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>141</v>
       </c>
@@ -4882,16 +6429,28 @@
         <v>0</v>
       </c>
       <c r="F129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G129">
-        <v>2</v>
-      </c>
-      <c r="K129" t="s">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>2</v>
+      </c>
+      <c r="N129" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O129" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -4908,13 +6467,25 @@
         <v>0</v>
       </c>
       <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
         <v>3</v>
       </c>
-      <c r="G130">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J130">
+        <v>2</v>
+      </c>
+      <c r="O130" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>143</v>
       </c>
@@ -4931,13 +6502,25 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>147</v>
       </c>
@@ -4954,13 +6537,25 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G132">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
+      </c>
+      <c r="J132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>148</v>
       </c>
@@ -4977,16 +6572,28 @@
         <v>0</v>
       </c>
       <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
         <v>3</v>
       </c>
-      <c r="G133">
-        <v>2</v>
-      </c>
-      <c r="K133" t="s">
+      <c r="J133">
+        <v>2</v>
+      </c>
+      <c r="N133" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O133" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>146</v>
       </c>
@@ -5003,13 +6610,25 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>150</v>
       </c>
@@ -5026,22 +6645,34 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
         <v>3</v>
       </c>
-      <c r="H135" t="s">
+      <c r="K135" t="s">
         <v>151</v>
       </c>
-      <c r="I135" t="s">
+      <c r="L135" t="s">
         <v>152</v>
       </c>
-      <c r="J135" t="s">
+      <c r="M135" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O135" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -5058,13 +6689,25 @@
         <v>0</v>
       </c>
       <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
         <v>3</v>
       </c>
-      <c r="G136">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J136">
+        <v>2</v>
+      </c>
+      <c r="O136" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>127</v>
       </c>
@@ -5081,13 +6724,25 @@
         <v>0</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>149</v>
       </c>
@@ -5104,13 +6759,25 @@
         <v>0</v>
       </c>
       <c r="F138">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>2</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -5127,16 +6794,28 @@
         <v>0</v>
       </c>
       <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
         <v>3</v>
       </c>
-      <c r="G139">
-        <v>2</v>
-      </c>
-      <c r="K139" t="s">
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="N139" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O139" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -5153,16 +6832,28 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140">
-        <v>1</v>
-      </c>
-      <c r="K140" t="s">
+        <v>0</v>
+      </c>
+      <c r="H140" t="s">
+        <v>260</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="N140" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O140" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>151</v>
       </c>
@@ -5179,13 +6870,25 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="O141" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -5202,13 +6905,25 @@
         <v>0</v>
       </c>
       <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
         <v>3</v>
       </c>
-      <c r="G142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="O142" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>153</v>
       </c>
@@ -5225,13 +6940,25 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>156</v>
       </c>
@@ -5248,16 +6975,28 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G144">
-        <v>2</v>
-      </c>
-      <c r="K144" t="s">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="J144">
+        <v>2</v>
+      </c>
+      <c r="N144" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O144" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>158</v>
       </c>
@@ -5274,13 +7013,25 @@
         <v>0</v>
       </c>
       <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
         <v>3</v>
       </c>
-      <c r="G145">
+      <c r="J145">
         <v>3</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O145" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -5297,13 +7048,25 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="O146" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -5320,13 +7083,25 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>2</v>
+      </c>
+      <c r="J147">
+        <v>2</v>
+      </c>
+      <c r="O147" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>138</v>
       </c>
@@ -5343,22 +7118,34 @@
         <v>0</v>
       </c>
       <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
         <v>3</v>
       </c>
-      <c r="G148">
-        <v>1</v>
-      </c>
-      <c r="H148" t="s">
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148" t="s">
         <v>162</v>
       </c>
-      <c r="I148" t="s">
+      <c r="L148" t="s">
         <v>163</v>
       </c>
-      <c r="J148" t="s">
+      <c r="M148" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O148" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>142</v>
       </c>
@@ -5375,13 +7162,25 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="O149" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>165</v>
       </c>
@@ -5398,13 +7197,25 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G150">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150">
+        <v>2</v>
+      </c>
+      <c r="O150" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>166</v>
       </c>
@@ -5421,13 +7232,25 @@
         <v>0</v>
       </c>
       <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
         <v>3</v>
       </c>
-      <c r="G151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="O151" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>167</v>
       </c>
@@ -5444,13 +7267,25 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="O152" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>168</v>
       </c>
@@ -5467,13 +7302,25 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="J153">
+        <v>2</v>
+      </c>
+      <c r="O153" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>162</v>
       </c>
@@ -5490,16 +7337,28 @@
         <v>0</v>
       </c>
       <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
         <v>3</v>
       </c>
-      <c r="G154">
-        <v>1</v>
-      </c>
-      <c r="K154" t="s">
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="N154" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O154" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>170</v>
       </c>
@@ -5516,13 +7375,25 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="O155" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>164</v>
       </c>
@@ -5539,13 +7410,25 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>2</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="O156" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -5562,13 +7445,25 @@
         <v>0</v>
       </c>
       <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
         <v>3</v>
       </c>
-      <c r="G157">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J157">
+        <v>2</v>
+      </c>
+      <c r="O157" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -5585,16 +7480,28 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>2</v>
-      </c>
-      <c r="K158" t="s">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>2</v>
+      </c>
+      <c r="N158" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O158" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>169</v>
       </c>
@@ -5611,22 +7518,34 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>1</v>
-      </c>
-      <c r="H159" t="s">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>2</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159" t="s">
         <v>174</v>
       </c>
-      <c r="I159" t="s">
+      <c r="L159" t="s">
         <v>175</v>
       </c>
-      <c r="J159" t="s">
+      <c r="M159" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O159" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>177</v>
       </c>
@@ -5643,22 +7562,34 @@
         <v>0</v>
       </c>
       <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
         <v>3</v>
       </c>
-      <c r="G160">
-        <v>1</v>
-      </c>
-      <c r="H160" t="s">
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160" t="s">
         <v>178</v>
       </c>
-      <c r="I160" t="s">
+      <c r="L160" t="s">
         <v>179</v>
       </c>
-      <c r="J160" t="s">
+      <c r="M160" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O160" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>152</v>
       </c>
@@ -5675,13 +7606,25 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>2</v>
+      </c>
+      <c r="O161" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>181</v>
       </c>
@@ -5698,13 +7641,25 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>2</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="O162" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>173</v>
       </c>
@@ -5721,13 +7676,25 @@
         <v>0</v>
       </c>
       <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
         <v>3</v>
       </c>
-      <c r="G163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="O163" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>182</v>
       </c>
@@ -5744,13 +7711,25 @@
         <v>0</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>2</v>
+      </c>
+      <c r="O164" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>174</v>
       </c>
@@ -5767,13 +7746,25 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165">
+        <v>2</v>
+      </c>
+      <c r="O165" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>178</v>
       </c>
@@ -5790,13 +7781,25 @@
         <v>0</v>
       </c>
       <c r="F166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
         <v>3</v>
       </c>
-      <c r="G166">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J166">
+        <v>2</v>
+      </c>
+      <c r="O166" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>176</v>
       </c>
@@ -5813,13 +7816,25 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>2</v>
+      </c>
+      <c r="O167" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>180</v>
       </c>
@@ -5836,13 +7851,25 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>2</v>
+      </c>
+      <c r="J168">
+        <v>2</v>
+      </c>
+      <c r="O168" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>183</v>
       </c>
@@ -5859,13 +7886,25 @@
         <v>0</v>
       </c>
       <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
         <v>3</v>
       </c>
-      <c r="G169">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J169">
+        <v>2</v>
+      </c>
+      <c r="O169" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>184</v>
       </c>
@@ -5882,16 +7921,28 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170">
-        <v>1</v>
-      </c>
-      <c r="K170" t="s">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="N170" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O170" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>186</v>
       </c>
@@ -5908,13 +7959,25 @@
         <v>0</v>
       </c>
       <c r="F171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>2</v>
+      </c>
+      <c r="J171">
+        <v>2</v>
+      </c>
+      <c r="O171" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>187</v>
       </c>
@@ -5931,22 +7994,34 @@
         <v>0</v>
       </c>
       <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
         <v>3</v>
       </c>
-      <c r="G172">
-        <v>2</v>
-      </c>
-      <c r="H172" t="s">
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172" t="s">
         <v>188</v>
       </c>
-      <c r="I172" t="s">
+      <c r="L172" t="s">
         <v>189</v>
       </c>
-      <c r="J172" t="s">
+      <c r="M172" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O172" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>191</v>
       </c>
@@ -5963,13 +8038,25 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>163</v>
       </c>
@@ -5986,16 +8073,28 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174">
-        <v>2</v>
-      </c>
-      <c r="K174" t="s">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>2</v>
+      </c>
+      <c r="J174">
+        <v>2</v>
+      </c>
+      <c r="N174" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O174" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>185</v>
       </c>
@@ -6012,13 +8111,25 @@
         <v>0</v>
       </c>
       <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
         <v>3</v>
       </c>
-      <c r="G175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="O175" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>193</v>
       </c>
@@ -6038,10 +8149,22 @@
         <v>1</v>
       </c>
       <c r="G176">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>2</v>
+      </c>
+      <c r="O176" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>194</v>
       </c>
@@ -6058,13 +8181,25 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>2</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>188</v>
       </c>
@@ -6081,13 +8216,25 @@
         <v>0</v>
       </c>
       <c r="F178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
         <v>3</v>
       </c>
-      <c r="G178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>192</v>
       </c>
@@ -6104,13 +8251,25 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>2</v>
+      </c>
+      <c r="O179" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -6127,13 +8286,25 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>2</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="O180" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>195</v>
       </c>
@@ -6150,13 +8321,25 @@
         <v>0</v>
       </c>
       <c r="F181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
         <v>3</v>
       </c>
-      <c r="G181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="O181" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>196</v>
       </c>
@@ -6173,13 +8356,25 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
         <v>3</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O182" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>197</v>
       </c>
@@ -6196,13 +8391,25 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>2</v>
+      </c>
+      <c r="J183">
+        <v>2</v>
+      </c>
+      <c r="O183" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>198</v>
       </c>
@@ -6219,16 +8426,28 @@
         <v>0</v>
       </c>
       <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
         <v>3</v>
       </c>
-      <c r="G184">
-        <v>1</v>
-      </c>
-      <c r="K184" t="s">
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="N184" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O184" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>175</v>
       </c>
@@ -6245,13 +8464,25 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="O185" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>179</v>
       </c>
@@ -6268,13 +8499,25 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>2</v>
+      </c>
+      <c r="J186">
         <v>3</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O186" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>200</v>
       </c>
@@ -6291,13 +8534,25 @@
         <v>0</v>
       </c>
       <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
         <v>3</v>
       </c>
-      <c r="G187">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="O187" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>201</v>
       </c>
@@ -6314,16 +8569,28 @@
         <v>0</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>1</v>
-      </c>
-      <c r="K188" t="s">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="N188" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O188" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -6340,13 +8607,25 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G189">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>2</v>
+      </c>
+      <c r="J189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>203</v>
       </c>
@@ -6363,13 +8642,25 @@
         <v>0</v>
       </c>
       <c r="F190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
         <v>3</v>
       </c>
-      <c r="G190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>204</v>
       </c>
@@ -6386,13 +8677,25 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>205</v>
       </c>
@@ -6409,22 +8712,34 @@
         <v>0</v>
       </c>
       <c r="F192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>1</v>
-      </c>
-      <c r="H192" t="s">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>2</v>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192" t="s">
         <v>189</v>
       </c>
-      <c r="I192" t="s">
+      <c r="L192" t="s">
         <v>206</v>
       </c>
-      <c r="J192" t="s">
+      <c r="M192" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="O192" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>202</v>
       </c>
@@ -6441,13 +8756,25 @@
         <v>0</v>
       </c>
       <c r="F193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
         <v>3</v>
       </c>
-      <c r="G193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>208</v>
       </c>
@@ -6464,13 +8791,25 @@
         <v>0</v>
       </c>
       <c r="F194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="O194" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>209</v>
       </c>
@@ -6487,13 +8826,25 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>2</v>
+      </c>
+      <c r="J195">
+        <v>2</v>
+      </c>
+      <c r="O195" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>210</v>
       </c>
@@ -6510,13 +8861,25 @@
         <v>0</v>
       </c>
       <c r="F196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
         <v>3</v>
       </c>
-      <c r="G196">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J196">
+        <v>2</v>
+      </c>
+      <c r="O196" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>211</v>
       </c>
@@ -6533,13 +8896,25 @@
         <v>0</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
         <v>3</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="O197" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>189</v>
       </c>
@@ -6556,13 +8931,25 @@
         <v>0</v>
       </c>
       <c r="F198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G198">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
+        <v>2</v>
+      </c>
+      <c r="O198" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>212</v>
       </c>
@@ -6579,13 +8966,25 @@
         <v>0</v>
       </c>
       <c r="F199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
         <v>3</v>
       </c>
-      <c r="G199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="O199" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -6602,22 +9001,34 @@
         <v>0</v>
       </c>
       <c r="F200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>2</v>
-      </c>
-      <c r="H200" t="s">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>2</v>
+      </c>
+      <c r="K200" t="s">
         <v>213</v>
       </c>
-      <c r="I200" t="s">
+      <c r="L200" t="s">
         <v>214</v>
       </c>
-      <c r="J200" t="s">
+      <c r="M200" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="O200" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>216</v>
       </c>
@@ -6634,13 +9045,25 @@
         <v>0</v>
       </c>
       <c r="F201">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
+        <v>2</v>
+      </c>
+      <c r="O201" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>217</v>
       </c>
@@ -6657,13 +9080,25 @@
         <v>0</v>
       </c>
       <c r="F202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
         <v>3</v>
       </c>
-      <c r="G202">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>218</v>
       </c>
@@ -6680,13 +9115,25 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203">
         <v>3</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="O203" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>219</v>
       </c>
@@ -6703,13 +9150,25 @@
         <v>0</v>
       </c>
       <c r="F204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>2</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="O204" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>220</v>
       </c>
@@ -6726,13 +9185,25 @@
         <v>0</v>
       </c>
       <c r="F205">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
         <v>3</v>
       </c>
-      <c r="G205">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J205">
+        <v>2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -6749,13 +9220,25 @@
         <v>0</v>
       </c>
       <c r="F206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
         <v>3</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="O206" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>221</v>
       </c>
@@ -6772,13 +9255,25 @@
         <v>0</v>
       </c>
       <c r="F207">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G207">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>2</v>
+      </c>
+      <c r="J207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -6795,13 +9290,25 @@
         <v>0</v>
       </c>
       <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
         <v>3</v>
       </c>
-      <c r="G208">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>222</v>
       </c>
@@ -6818,13 +9325,25 @@
         <v>0</v>
       </c>
       <c r="F209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="O209" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>223</v>
       </c>
@@ -6841,13 +9360,25 @@
         <v>0</v>
       </c>
       <c r="F210">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>2</v>
+      </c>
+      <c r="J210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>224</v>
       </c>
@@ -6864,22 +9395,34 @@
         <v>0</v>
       </c>
       <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
         <v>3</v>
       </c>
-      <c r="G211">
-        <v>1</v>
-      </c>
-      <c r="H211" t="s">
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211" t="s">
         <v>225</v>
       </c>
-      <c r="J211" t="s">
+      <c r="M211" t="s">
         <v>226</v>
       </c>
-      <c r="K211" t="s">
+      <c r="N211" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O211" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>228</v>
       </c>
@@ -6896,19 +9439,31 @@
         <v>0</v>
       </c>
       <c r="F212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>2</v>
-      </c>
-      <c r="H212" t="s">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>2</v>
+      </c>
+      <c r="K212" t="s">
         <v>206</v>
       </c>
-      <c r="J212" t="s">
+      <c r="M212" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O212" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>230</v>
       </c>
@@ -6925,13 +9480,25 @@
         <v>0</v>
       </c>
       <c r="F213">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>2</v>
+      </c>
+      <c r="J213">
+        <v>2</v>
+      </c>
+      <c r="O213" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>231</v>
       </c>
@@ -6948,13 +9515,25 @@
         <v>0</v>
       </c>
       <c r="F214">
+        <v>0</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+      <c r="I214">
         <v>3</v>
       </c>
-      <c r="G214">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J214">
+        <v>2</v>
+      </c>
+      <c r="O214" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>232</v>
       </c>
@@ -6971,16 +9550,28 @@
         <v>0</v>
       </c>
       <c r="F215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
         <v>3</v>
       </c>
-      <c r="K215" t="s">
+      <c r="N215" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O215" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>227</v>
       </c>
@@ -6997,13 +9588,25 @@
         <v>0</v>
       </c>
       <c r="F216">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>2</v>
+      </c>
+      <c r="J216">
+        <v>2</v>
+      </c>
+      <c r="O216" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>225</v>
       </c>
@@ -7020,13 +9623,25 @@
         <v>0</v>
       </c>
       <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
         <v>3</v>
       </c>
-      <c r="G217">
+      <c r="J217">
         <v>3</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O217" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>206</v>
       </c>
@@ -7043,13 +9658,25 @@
         <v>0</v>
       </c>
       <c r="F218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>226</v>
       </c>
@@ -7066,13 +9693,25 @@
         <v>0</v>
       </c>
       <c r="F219">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>2</v>
+      </c>
+      <c r="J219">
+        <v>2</v>
+      </c>
+      <c r="O219" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>229</v>
       </c>
@@ -7089,13 +9728,25 @@
         <v>0</v>
       </c>
       <c r="F220">
+        <v>0</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
         <v>3</v>
       </c>
-      <c r="G220">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>233</v>
       </c>
@@ -7112,13 +9763,25 @@
         <v>0</v>
       </c>
       <c r="F221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>2</v>
+      </c>
+      <c r="O221" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>234</v>
       </c>
@@ -7135,13 +9798,25 @@
         <v>0</v>
       </c>
       <c r="F222">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G222">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>2</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>235</v>
       </c>
@@ -7158,13 +9833,25 @@
         <v>0</v>
       </c>
       <c r="F223">
+        <v>0</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
         <v>3</v>
       </c>
-      <c r="G223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>236</v>
       </c>
@@ -7181,19 +9868,31 @@
         <v>0</v>
       </c>
       <c r="F224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G224">
-        <v>2</v>
-      </c>
-      <c r="H224" t="s">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>2</v>
+      </c>
+      <c r="K224" t="s">
         <v>237</v>
       </c>
-      <c r="J224" t="s">
+      <c r="M224" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O224" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>239</v>
       </c>
@@ -7210,16 +9909,28 @@
         <v>0</v>
       </c>
       <c r="F225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G225">
-        <v>2</v>
-      </c>
-      <c r="K225" t="s">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>2</v>
+      </c>
+      <c r="J225">
+        <v>2</v>
+      </c>
+      <c r="N225" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O225" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>214</v>
       </c>
@@ -7236,13 +9947,25 @@
         <v>0</v>
       </c>
       <c r="F226">
+        <v>0</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
         <v>3</v>
       </c>
-      <c r="G226">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>240</v>
       </c>
@@ -7259,13 +9982,25 @@
         <v>0</v>
       </c>
       <c r="F227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>241</v>
       </c>
@@ -7282,13 +10017,25 @@
         <v>0</v>
       </c>
       <c r="F228">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>2</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>242</v>
       </c>
@@ -7305,16 +10052,28 @@
         <v>0</v>
       </c>
       <c r="F229">
+        <v>0</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
         <v>3</v>
       </c>
-      <c r="G229">
-        <v>2</v>
-      </c>
-      <c r="K229" t="s">
+      <c r="J229">
+        <v>2</v>
+      </c>
+      <c r="N229" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O229" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>237</v>
       </c>
@@ -7331,13 +10090,25 @@
         <v>0</v>
       </c>
       <c r="F230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G230">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="O230" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>244</v>
       </c>
@@ -7354,13 +10125,25 @@
         <v>0</v>
       </c>
       <c r="F231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G231">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>2</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="O231" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>238</v>
       </c>
@@ -7377,13 +10160,25 @@
         <v>0</v>
       </c>
       <c r="F232">
+        <v>0</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
         <v>3</v>
       </c>
-      <c r="G232">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="O232" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>245</v>
       </c>
@@ -7400,13 +10195,25 @@
         <v>0</v>
       </c>
       <c r="F233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>2</v>
+      </c>
+      <c r="O233" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>243</v>
       </c>
@@ -7423,16 +10230,28 @@
         <v>0</v>
       </c>
       <c r="F234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G234">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>2</v>
+      </c>
+      <c r="J234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K234" xr:uid="{041A12D7-D1F2-5E4A-959D-815F4F1F9005}"/>
+  <autoFilter ref="A1:N234" xr:uid="{041A12D7-D1F2-5E4A-959D-815F4F1F9005}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:K1048576" xr:uid="{836F0146-E07F-2A4C-BD11-FE221837FD18}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:N1048576" xr:uid="{836F0146-E07F-2A4C-BD11-FE221837FD18}">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -7442,10 +10261,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3EBCD07-DD53-1747-8BBC-A1CAD3C527A9}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>246</v>
       </c>
@@ -7459,20 +10278,26 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>250</v>
       </c>
@@ -7480,10 +10305,13 @@
         <v>1</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>251</v>
       </c>
@@ -7491,15 +10319,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>252</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7507,7 +10338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -7515,7 +10346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>253</v>
       </c>
@@ -7523,12 +10354,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>255</v>
       </c>

--- a/Liste.xlsx
+++ b/Liste.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordiordonezadellach/Desktop/Projectes/Classes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2388E678-873D-E748-AA77-C5A051FA4437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA63A642-63F1-2D42-98A0-F1582E336B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1840" yWindow="-20560" windowWidth="28040" windowHeight="15820" xr2:uid="{B5B86117-F7DA-9D45-88D5-7A78429F12FC}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="classes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">liste!$A$1:$N$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">liste!$A$1:$O$234</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="263">
   <si>
     <t>Elèves à affecter</t>
   </si>
@@ -819,14 +819,20 @@
     <t>Origine</t>
   </si>
   <si>
-    <t>1+H140</t>
+    <t>sans3</t>
+  </si>
+  <si>
+    <t>sans4</t>
+  </si>
+  <si>
+    <t>sans5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -957,6 +963,12 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1680,10 +1692,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041A12D7-D1F2-5E4A-959D-815F4F1F9005}">
-  <dimension ref="A1:O234"/>
+  <dimension ref="A1:R234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1727,10 +1739,19 @@
         <v>10</v>
       </c>
       <c r="O1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>262</v>
+      </c>
+      <c r="R1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1770,11 +1791,20 @@
       <c r="M2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" t="s">
+      <c r="N2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1805,14 +1835,14 @@
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>13</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1843,11 +1873,11 @@
       <c r="J4">
         <v>3</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1878,11 +1908,11 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="O5" t="s">
+      <c r="R5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1922,11 +1952,20 @@
       <c r="M6" t="s">
         <v>23</v>
       </c>
-      <c r="O6" t="s">
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1957,14 +1996,14 @@
       <c r="J7">
         <v>2</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>21</v>
       </c>
-      <c r="O7" t="s">
+      <c r="R7" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1995,11 +2034,11 @@
       <c r="J8">
         <v>2</v>
       </c>
-      <c r="O8" t="s">
+      <c r="R8" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2030,11 +2069,11 @@
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="O9" t="s">
+      <c r="R9" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -2065,11 +2104,11 @@
       <c r="J10">
         <v>2</v>
       </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2109,11 +2148,20 @@
       <c r="M11" t="s">
         <v>29</v>
       </c>
-      <c r="O11" t="s">
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2130,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2144,11 +2192,11 @@
       <c r="J12">
         <v>2</v>
       </c>
-      <c r="O12" t="s">
+      <c r="R12" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2179,11 +2227,11 @@
       <c r="J13">
         <v>2</v>
       </c>
-      <c r="O13" t="s">
+      <c r="R13" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2223,11 +2271,20 @@
       <c r="M14" t="s">
         <v>33</v>
       </c>
-      <c r="O14" t="s">
+      <c r="N14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>33</v>
+      </c>
+      <c r="R14" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2267,11 +2324,20 @@
       <c r="M15" t="s">
         <v>37</v>
       </c>
-      <c r="O15" t="s">
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2302,11 +2368,11 @@
       <c r="J16">
         <v>2</v>
       </c>
-      <c r="O16" t="s">
+      <c r="R16" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2337,14 +2403,14 @@
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>33</v>
       </c>
-      <c r="O17" t="s">
+      <c r="R17" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2375,11 +2441,11 @@
       <c r="J18">
         <v>1</v>
       </c>
-      <c r="O18" t="s">
+      <c r="R18" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2410,11 +2476,11 @@
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="O19" t="s">
+      <c r="R19" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2445,11 +2511,11 @@
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="O20" t="s">
+      <c r="R20" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2490,13 +2556,22 @@
         <v>42</v>
       </c>
       <c r="N21" t="s">
+        <v>42</v>
+      </c>
+      <c r="O21" t="s">
         <v>43</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>42</v>
+      </c>
+      <c r="R21" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2527,11 +2602,11 @@
       <c r="J22">
         <v>1</v>
       </c>
-      <c r="O22" t="s">
+      <c r="R22" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2562,11 +2637,11 @@
       <c r="J23">
         <v>2</v>
       </c>
-      <c r="O23" t="s">
+      <c r="R23" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -2597,14 +2672,14 @@
       <c r="J24">
         <v>1</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>42</v>
       </c>
-      <c r="O24" t="s">
+      <c r="R24" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -2635,11 +2710,11 @@
       <c r="J25">
         <v>1</v>
       </c>
-      <c r="O25" t="s">
+      <c r="R25" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -2679,11 +2754,20 @@
       <c r="M26" t="s">
         <v>47</v>
       </c>
-      <c r="O26" t="s">
+      <c r="N26" t="s">
+        <v>47</v>
+      </c>
+      <c r="P26" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>47</v>
+      </c>
+      <c r="R26" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -2714,11 +2798,11 @@
       <c r="J27">
         <v>2</v>
       </c>
-      <c r="O27" t="s">
+      <c r="R27" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2749,14 +2833,14 @@
       <c r="J28">
         <v>2</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>48</v>
       </c>
-      <c r="O28" t="s">
+      <c r="R28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2787,11 +2871,11 @@
       <c r="J29">
         <v>2</v>
       </c>
-      <c r="O29" t="s">
+      <c r="R29" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2822,11 +2906,11 @@
       <c r="J30">
         <v>1</v>
       </c>
-      <c r="O30" t="s">
+      <c r="R30" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -2857,11 +2941,11 @@
       <c r="J31">
         <v>2</v>
       </c>
-      <c r="O31" t="s">
+      <c r="R31" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -2892,11 +2976,11 @@
       <c r="J32">
         <v>2</v>
       </c>
-      <c r="O32" t="s">
+      <c r="R32" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -2936,11 +3020,20 @@
       <c r="M33" t="s">
         <v>36</v>
       </c>
-      <c r="O33" t="s">
+      <c r="N33" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>36</v>
+      </c>
+      <c r="R33" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2971,11 +3064,11 @@
       <c r="J34">
         <v>2</v>
       </c>
-      <c r="O34" t="s">
+      <c r="R34" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -3006,11 +3099,11 @@
       <c r="J35">
         <v>2</v>
       </c>
-      <c r="O35" t="s">
+      <c r="R35" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -3041,11 +3134,11 @@
       <c r="J36">
         <v>3</v>
       </c>
-      <c r="O36" t="s">
+      <c r="R36" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -3076,11 +3169,11 @@
       <c r="J37">
         <v>2</v>
       </c>
-      <c r="O37" t="s">
+      <c r="R37" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -3111,14 +3204,14 @@
       <c r="J38">
         <v>2</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>56</v>
       </c>
-      <c r="O38" t="s">
+      <c r="R38" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -3149,11 +3242,11 @@
       <c r="J39">
         <v>3</v>
       </c>
-      <c r="O39" t="s">
+      <c r="R39" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -3184,11 +3277,11 @@
       <c r="J40">
         <v>2</v>
       </c>
-      <c r="O40" t="s">
+      <c r="R40" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>36</v>
       </c>
@@ -3219,11 +3312,11 @@
       <c r="J41">
         <v>1</v>
       </c>
-      <c r="O41" t="s">
+      <c r="R41" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>57</v>
       </c>
@@ -3254,14 +3347,14 @@
       <c r="J42">
         <v>2</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>41</v>
       </c>
-      <c r="O42" t="s">
+      <c r="R42" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -3292,11 +3385,11 @@
       <c r="J43">
         <v>3</v>
       </c>
-      <c r="O43" t="s">
+      <c r="R43" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -3336,11 +3429,20 @@
       <c r="M44" t="s">
         <v>46</v>
       </c>
-      <c r="O44" t="s">
+      <c r="N44" t="s">
+        <v>46</v>
+      </c>
+      <c r="P44" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>46</v>
+      </c>
+      <c r="R44" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -3381,13 +3483,22 @@
         <v>64</v>
       </c>
       <c r="N45" t="s">
+        <v>64</v>
+      </c>
+      <c r="O45" t="s">
         <v>59</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>64</v>
+      </c>
+      <c r="R45" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -3418,11 +3529,11 @@
       <c r="J46">
         <v>1</v>
       </c>
-      <c r="O46" t="s">
+      <c r="R46" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -3453,11 +3564,11 @@
       <c r="J47">
         <v>2</v>
       </c>
-      <c r="O47" t="s">
+      <c r="R47" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -3488,11 +3599,11 @@
       <c r="J48">
         <v>2</v>
       </c>
-      <c r="O48" t="s">
+      <c r="R48" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -3523,14 +3634,14 @@
       <c r="J49">
         <v>2</v>
       </c>
-      <c r="N49" t="s">
+      <c r="O49" t="s">
         <v>68</v>
       </c>
-      <c r="O49" t="s">
+      <c r="R49" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -3561,11 +3672,11 @@
       <c r="J50">
         <v>3</v>
       </c>
-      <c r="O50" t="s">
+      <c r="R50" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -3596,11 +3707,11 @@
       <c r="J51">
         <v>2</v>
       </c>
-      <c r="O51" t="s">
+      <c r="R51" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -3631,11 +3742,11 @@
       <c r="J52">
         <v>2</v>
       </c>
-      <c r="O52" t="s">
+      <c r="R52" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -3666,11 +3777,11 @@
       <c r="J53">
         <v>1</v>
       </c>
-      <c r="O53" t="s">
+      <c r="R53" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -3701,11 +3812,11 @@
       <c r="J54">
         <v>1</v>
       </c>
-      <c r="O54" t="s">
+      <c r="R54" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -3736,11 +3847,11 @@
       <c r="J55">
         <v>1</v>
       </c>
-      <c r="O55" t="s">
+      <c r="R55" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -3771,11 +3882,11 @@
       <c r="J56">
         <v>1</v>
       </c>
-      <c r="O56" t="s">
+      <c r="R56" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -3815,11 +3926,20 @@
       <c r="M57" t="s">
         <v>74</v>
       </c>
-      <c r="O57" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N57" t="s">
+        <v>74</v>
+      </c>
+      <c r="P57" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>74</v>
+      </c>
+      <c r="R57" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3850,11 +3970,11 @@
       <c r="J58">
         <v>2</v>
       </c>
-      <c r="O58" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R58" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -3885,14 +4005,14 @@
       <c r="J59">
         <v>2</v>
       </c>
-      <c r="N59" t="s">
+      <c r="O59" t="s">
         <v>76</v>
       </c>
-      <c r="O59" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R59" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -3932,11 +4052,20 @@
       <c r="M60" t="s">
         <v>80</v>
       </c>
-      <c r="O60" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N60" t="s">
+        <v>80</v>
+      </c>
+      <c r="P60" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>80</v>
+      </c>
+      <c r="R60" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -3967,11 +4096,11 @@
       <c r="J61">
         <v>1</v>
       </c>
-      <c r="O61" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R61" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -4002,11 +4131,11 @@
       <c r="J62">
         <v>2</v>
       </c>
-      <c r="O62" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R62" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -4037,14 +4166,14 @@
       <c r="J63">
         <v>2</v>
       </c>
-      <c r="N63" t="s">
+      <c r="O63" t="s">
         <v>80</v>
       </c>
-      <c r="O63" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R63" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -4075,11 +4204,11 @@
       <c r="J64">
         <v>1</v>
       </c>
-      <c r="O64" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R64" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -4110,11 +4239,11 @@
       <c r="J65">
         <v>2</v>
       </c>
-      <c r="O65" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R65" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>78</v>
       </c>
@@ -4145,11 +4274,11 @@
       <c r="J66">
         <v>1</v>
       </c>
-      <c r="O66" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R66" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -4180,11 +4309,11 @@
       <c r="J67">
         <v>2</v>
       </c>
-      <c r="O67" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R67" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -4215,11 +4344,11 @@
       <c r="J68">
         <v>2</v>
       </c>
-      <c r="O68" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R68" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>84</v>
       </c>
@@ -4250,14 +4379,14 @@
       <c r="J69">
         <v>2</v>
       </c>
-      <c r="N69" t="s">
+      <c r="O69" t="s">
         <v>85</v>
       </c>
-      <c r="O69" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R69" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>60</v>
       </c>
@@ -4288,11 +4417,11 @@
       <c r="J70">
         <v>1</v>
       </c>
-      <c r="O70" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R70" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -4332,11 +4461,20 @@
       <c r="M71" t="s">
         <v>88</v>
       </c>
-      <c r="O71" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N71" t="s">
+        <v>88</v>
+      </c>
+      <c r="P71" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>88</v>
+      </c>
+      <c r="R71" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -4367,11 +4505,11 @@
       <c r="J72">
         <v>3</v>
       </c>
-      <c r="O72" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R72" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -4402,14 +4540,14 @@
       <c r="J73">
         <v>1</v>
       </c>
-      <c r="N73" t="s">
+      <c r="O73" t="s">
         <v>91</v>
       </c>
-      <c r="O73" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R73" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -4440,11 +4578,11 @@
       <c r="J74">
         <v>3</v>
       </c>
-      <c r="O74" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R74" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -4475,11 +4613,11 @@
       <c r="J75">
         <v>2</v>
       </c>
-      <c r="O75" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R75" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -4510,11 +4648,11 @@
       <c r="J76">
         <v>1</v>
       </c>
-      <c r="O76" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R76" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -4545,11 +4683,11 @@
       <c r="J77">
         <v>2</v>
       </c>
-      <c r="O77" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R77" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>91</v>
       </c>
@@ -4580,11 +4718,11 @@
       <c r="J78">
         <v>1</v>
       </c>
-      <c r="O78" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R78" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -4615,11 +4753,11 @@
       <c r="J79">
         <v>1</v>
       </c>
-      <c r="O79" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R79" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -4650,11 +4788,11 @@
       <c r="J80">
         <v>2</v>
       </c>
-      <c r="O80" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R80" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -4685,11 +4823,11 @@
       <c r="J81">
         <v>1</v>
       </c>
-      <c r="O81" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R81" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -4720,11 +4858,11 @@
       <c r="J82">
         <v>2</v>
       </c>
-      <c r="O82" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R82" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -4755,14 +4893,14 @@
       <c r="J83">
         <v>1</v>
       </c>
-      <c r="N83" t="s">
+      <c r="O83" t="s">
         <v>97</v>
       </c>
-      <c r="O83" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R83" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -4802,11 +4940,20 @@
       <c r="M84" t="s">
         <v>101</v>
       </c>
-      <c r="O84" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N84" t="s">
+        <v>101</v>
+      </c>
+      <c r="P84" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>101</v>
+      </c>
+      <c r="R84" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -4837,11 +4984,11 @@
       <c r="J85">
         <v>1</v>
       </c>
-      <c r="O85" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R85" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -4872,11 +5019,11 @@
       <c r="J86">
         <v>2</v>
       </c>
-      <c r="O86" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R86" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>103</v>
       </c>
@@ -4907,14 +5054,14 @@
       <c r="J87">
         <v>1</v>
       </c>
-      <c r="N87" t="s">
+      <c r="O87" t="s">
         <v>101</v>
       </c>
-      <c r="O87" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R87" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -4945,11 +5092,11 @@
       <c r="J88">
         <v>3</v>
       </c>
-      <c r="O88" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R88" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>104</v>
       </c>
@@ -4980,11 +5127,11 @@
       <c r="J89">
         <v>3</v>
       </c>
-      <c r="O89" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R89" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -5015,14 +5162,14 @@
       <c r="J90">
         <v>1</v>
       </c>
-      <c r="N90" t="s">
+      <c r="O90" t="s">
         <v>105</v>
       </c>
-      <c r="O90" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R90" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>106</v>
       </c>
@@ -5053,11 +5200,11 @@
       <c r="J91">
         <v>2</v>
       </c>
-      <c r="O91" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R91" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -5088,11 +5235,11 @@
       <c r="J92">
         <v>2</v>
       </c>
-      <c r="O92" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R92" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -5123,11 +5270,11 @@
       <c r="J93">
         <v>1</v>
       </c>
-      <c r="O93" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R93" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -5158,14 +5305,14 @@
       <c r="J94">
         <v>2</v>
       </c>
-      <c r="N94" t="s">
+      <c r="O94" t="s">
         <v>109</v>
       </c>
-      <c r="O94" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>105</v>
       </c>
@@ -5196,11 +5343,11 @@
       <c r="J95">
         <v>1</v>
       </c>
-      <c r="O95" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R95" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -5231,11 +5378,11 @@
       <c r="J96">
         <v>3</v>
       </c>
-      <c r="O96" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R96" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>87</v>
       </c>
@@ -5266,11 +5413,11 @@
       <c r="J97">
         <v>2</v>
       </c>
-      <c r="O97" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R97" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -5310,11 +5457,20 @@
       <c r="M98" t="s">
         <v>114</v>
       </c>
-      <c r="O98" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N98" t="s">
+        <v>114</v>
+      </c>
+      <c r="P98" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>114</v>
+      </c>
+      <c r="R98" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -5345,11 +5501,11 @@
       <c r="J99">
         <v>2</v>
       </c>
-      <c r="O99" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R99" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>115</v>
       </c>
@@ -5380,11 +5536,11 @@
       <c r="J100">
         <v>2</v>
       </c>
-      <c r="O100" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R100" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>116</v>
       </c>
@@ -5424,11 +5580,20 @@
       <c r="M101" t="s">
         <v>119</v>
       </c>
-      <c r="O101" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N101" t="s">
+        <v>119</v>
+      </c>
+      <c r="P101" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>119</v>
+      </c>
+      <c r="R101" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>120</v>
       </c>
@@ -5459,11 +5624,11 @@
       <c r="J102">
         <v>2</v>
       </c>
-      <c r="O102" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R102" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>121</v>
       </c>
@@ -5494,11 +5659,11 @@
       <c r="J103">
         <v>2</v>
       </c>
-      <c r="O103" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R103" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>112</v>
       </c>
@@ -5529,14 +5694,14 @@
       <c r="J104">
         <v>1</v>
       </c>
-      <c r="N104" t="s">
+      <c r="O104" t="s">
         <v>119</v>
       </c>
-      <c r="O104" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R104" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -5567,11 +5732,11 @@
       <c r="J105">
         <v>1</v>
       </c>
-      <c r="O105" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R105" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -5602,11 +5767,11 @@
       <c r="J106">
         <v>1</v>
       </c>
-      <c r="O106" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R106" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>117</v>
       </c>
@@ -5637,11 +5802,11 @@
       <c r="J107">
         <v>1</v>
       </c>
-      <c r="O107" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R107" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>123</v>
       </c>
@@ -5672,14 +5837,14 @@
       <c r="J108">
         <v>2</v>
       </c>
-      <c r="N108" t="s">
+      <c r="O108" t="s">
         <v>124</v>
       </c>
-      <c r="O108" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R108" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>119</v>
       </c>
@@ -5710,11 +5875,11 @@
       <c r="J109">
         <v>1</v>
       </c>
-      <c r="O109" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R109" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>100</v>
       </c>
@@ -5745,11 +5910,11 @@
       <c r="J110">
         <v>1</v>
       </c>
-      <c r="O110" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R110" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -5789,11 +5954,20 @@
       <c r="M111" t="s">
         <v>128</v>
       </c>
-      <c r="O111" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N111" t="s">
+        <v>128</v>
+      </c>
+      <c r="P111" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>128</v>
+      </c>
+      <c r="R111" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>129</v>
       </c>
@@ -5824,11 +5998,11 @@
       <c r="J112">
         <v>2</v>
       </c>
-      <c r="O112" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R112" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>124</v>
       </c>
@@ -5859,11 +6033,11 @@
       <c r="J113">
         <v>1</v>
       </c>
-      <c r="O113" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R113" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>130</v>
       </c>
@@ -5894,11 +6068,11 @@
       <c r="J114">
         <v>2</v>
       </c>
-      <c r="O114" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R114" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>131</v>
       </c>
@@ -5929,14 +6103,14 @@
       <c r="J115">
         <v>2</v>
       </c>
-      <c r="N115" t="s">
+      <c r="O115" t="s">
         <v>132</v>
       </c>
-      <c r="O115" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R115" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>133</v>
       </c>
@@ -5967,11 +6141,11 @@
       <c r="J116">
         <v>2</v>
       </c>
-      <c r="O116" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R116" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -6002,11 +6176,11 @@
       <c r="J117">
         <v>1</v>
       </c>
-      <c r="O117" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R117" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -6037,11 +6211,11 @@
       <c r="J118">
         <v>2</v>
       </c>
-      <c r="O118" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R118" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>128</v>
       </c>
@@ -6072,14 +6246,14 @@
       <c r="J119">
         <v>1</v>
       </c>
-      <c r="N119" t="s">
+      <c r="O119" t="s">
         <v>113</v>
       </c>
-      <c r="O119" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R119" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>132</v>
       </c>
@@ -6110,11 +6284,11 @@
       <c r="J120">
         <v>3</v>
       </c>
-      <c r="O120" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R120" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -6145,11 +6319,11 @@
       <c r="J121">
         <v>1</v>
       </c>
-      <c r="O121" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R121" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -6189,11 +6363,20 @@
       <c r="M122" t="s">
         <v>139</v>
       </c>
-      <c r="O122" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N122" t="s">
+        <v>139</v>
+      </c>
+      <c r="P122" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>139</v>
+      </c>
+      <c r="R122" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>140</v>
       </c>
@@ -6233,11 +6416,20 @@
       <c r="M123" t="s">
         <v>143</v>
       </c>
-      <c r="O123" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N123" t="s">
+        <v>143</v>
+      </c>
+      <c r="P123" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>143</v>
+      </c>
+      <c r="R123" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>113</v>
       </c>
@@ -6268,11 +6460,11 @@
       <c r="J124">
         <v>2</v>
       </c>
-      <c r="O124" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R124" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>144</v>
       </c>
@@ -6303,11 +6495,11 @@
       <c r="J125">
         <v>1</v>
       </c>
-      <c r="O125" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R125" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>145</v>
       </c>
@@ -6338,11 +6530,11 @@
       <c r="J126">
         <v>1</v>
       </c>
-      <c r="O126" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R126" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>118</v>
       </c>
@@ -6373,11 +6565,11 @@
       <c r="J127">
         <v>2</v>
       </c>
-      <c r="O127" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R127" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>137</v>
       </c>
@@ -6408,11 +6600,11 @@
       <c r="J128">
         <v>1</v>
       </c>
-      <c r="O128" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R128" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>141</v>
       </c>
@@ -6443,14 +6635,14 @@
       <c r="J129">
         <v>2</v>
       </c>
-      <c r="N129" t="s">
+      <c r="O129" t="s">
         <v>146</v>
       </c>
-      <c r="O129" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R129" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -6481,11 +6673,11 @@
       <c r="J130">
         <v>2</v>
       </c>
-      <c r="O130" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R130" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>143</v>
       </c>
@@ -6516,11 +6708,11 @@
       <c r="J131">
         <v>2</v>
       </c>
-      <c r="O131" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R131" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>147</v>
       </c>
@@ -6551,11 +6743,11 @@
       <c r="J132">
         <v>2</v>
       </c>
-      <c r="O132" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R132" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>148</v>
       </c>
@@ -6586,14 +6778,14 @@
       <c r="J133">
         <v>2</v>
       </c>
-      <c r="N133" t="s">
+      <c r="O133" t="s">
         <v>149</v>
       </c>
-      <c r="O133" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R133" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>146</v>
       </c>
@@ -6624,11 +6816,11 @@
       <c r="J134">
         <v>1</v>
       </c>
-      <c r="O134" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R134" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>150</v>
       </c>
@@ -6668,11 +6860,20 @@
       <c r="M135" t="s">
         <v>153</v>
       </c>
-      <c r="O135" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N135" t="s">
+        <v>153</v>
+      </c>
+      <c r="P135" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>153</v>
+      </c>
+      <c r="R135" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -6703,11 +6904,11 @@
       <c r="J136">
         <v>2</v>
       </c>
-      <c r="O136" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R136" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>127</v>
       </c>
@@ -6738,11 +6939,11 @@
       <c r="J137">
         <v>2</v>
       </c>
-      <c r="O137" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R137" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>149</v>
       </c>
@@ -6773,11 +6974,11 @@
       <c r="J138">
         <v>1</v>
       </c>
-      <c r="O138" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R138" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -6808,14 +7009,14 @@
       <c r="J139">
         <v>2</v>
       </c>
-      <c r="N139" t="s">
+      <c r="O139" t="s">
         <v>156</v>
       </c>
-      <c r="O139" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R139" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -6837,8 +7038,8 @@
       <c r="G140">
         <v>0</v>
       </c>
-      <c r="H140" t="s">
-        <v>260</v>
+      <c r="H140">
+        <v>1</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -6846,14 +7047,14 @@
       <c r="J140">
         <v>1</v>
       </c>
-      <c r="N140" t="s">
+      <c r="O140" t="s">
         <v>158</v>
       </c>
-      <c r="O140" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R140" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>151</v>
       </c>
@@ -6884,11 +7085,11 @@
       <c r="J141">
         <v>2</v>
       </c>
-      <c r="O141" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R141" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -6919,11 +7120,11 @@
       <c r="J142">
         <v>1</v>
       </c>
-      <c r="O142" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R142" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>153</v>
       </c>
@@ -6954,11 +7155,11 @@
       <c r="J143">
         <v>1</v>
       </c>
-      <c r="O143" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R143" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>156</v>
       </c>
@@ -6989,14 +7190,14 @@
       <c r="J144">
         <v>2</v>
       </c>
-      <c r="N144" t="s">
+      <c r="O144" t="s">
         <v>142</v>
       </c>
-      <c r="O144" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R144" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>158</v>
       </c>
@@ -7027,11 +7228,11 @@
       <c r="J145">
         <v>3</v>
       </c>
-      <c r="O145" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R145" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -7062,11 +7263,11 @@
       <c r="J146">
         <v>2</v>
       </c>
-      <c r="O146" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R146" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -7097,11 +7298,11 @@
       <c r="J147">
         <v>2</v>
       </c>
-      <c r="O147" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R147" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>138</v>
       </c>
@@ -7141,11 +7342,20 @@
       <c r="M148" t="s">
         <v>164</v>
       </c>
-      <c r="O148" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N148" t="s">
+        <v>164</v>
+      </c>
+      <c r="P148" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>164</v>
+      </c>
+      <c r="R148" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>142</v>
       </c>
@@ -7176,11 +7386,11 @@
       <c r="J149">
         <v>1</v>
       </c>
-      <c r="O149" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R149" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>165</v>
       </c>
@@ -7211,11 +7421,11 @@
       <c r="J150">
         <v>2</v>
       </c>
-      <c r="O150" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R150" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>166</v>
       </c>
@@ -7246,11 +7456,11 @@
       <c r="J151">
         <v>1</v>
       </c>
-      <c r="O151" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R151" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>167</v>
       </c>
@@ -7281,11 +7491,11 @@
       <c r="J152">
         <v>1</v>
       </c>
-      <c r="O152" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R152" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>168</v>
       </c>
@@ -7316,11 +7526,11 @@
       <c r="J153">
         <v>2</v>
       </c>
-      <c r="O153" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R153" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>162</v>
       </c>
@@ -7351,14 +7561,14 @@
       <c r="J154">
         <v>1</v>
       </c>
-      <c r="N154" t="s">
+      <c r="O154" t="s">
         <v>169</v>
       </c>
-      <c r="O154" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R154" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>170</v>
       </c>
@@ -7389,11 +7599,11 @@
       <c r="J155">
         <v>2</v>
       </c>
-      <c r="O155" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R155" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>164</v>
       </c>
@@ -7424,11 +7634,11 @@
       <c r="J156">
         <v>2</v>
       </c>
-      <c r="O156" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R156" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -7459,11 +7669,11 @@
       <c r="J157">
         <v>2</v>
       </c>
-      <c r="O157" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R157" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -7494,14 +7704,14 @@
       <c r="J158">
         <v>2</v>
       </c>
-      <c r="N158" t="s">
+      <c r="O158" t="s">
         <v>173</v>
       </c>
-      <c r="O158" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R158" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>169</v>
       </c>
@@ -7541,11 +7751,20 @@
       <c r="M159" t="s">
         <v>176</v>
       </c>
-      <c r="O159" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N159" t="s">
+        <v>176</v>
+      </c>
+      <c r="P159" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>176</v>
+      </c>
+      <c r="R159" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>177</v>
       </c>
@@ -7585,11 +7804,20 @@
       <c r="M160" t="s">
         <v>180</v>
       </c>
-      <c r="O160" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N160" t="s">
+        <v>180</v>
+      </c>
+      <c r="P160" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>180</v>
+      </c>
+      <c r="R160" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>152</v>
       </c>
@@ -7620,11 +7848,11 @@
       <c r="J161">
         <v>2</v>
       </c>
-      <c r="O161" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R161" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>181</v>
       </c>
@@ -7655,11 +7883,11 @@
       <c r="J162">
         <v>1</v>
       </c>
-      <c r="O162" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R162" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>173</v>
       </c>
@@ -7690,11 +7918,11 @@
       <c r="J163">
         <v>1</v>
       </c>
-      <c r="O163" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R163" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>182</v>
       </c>
@@ -7725,11 +7953,11 @@
       <c r="J164">
         <v>2</v>
       </c>
-      <c r="O164" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R164" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>174</v>
       </c>
@@ -7760,11 +7988,11 @@
       <c r="J165">
         <v>2</v>
       </c>
-      <c r="O165" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R165" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>178</v>
       </c>
@@ -7795,11 +8023,11 @@
       <c r="J166">
         <v>2</v>
       </c>
-      <c r="O166" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R166" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>176</v>
       </c>
@@ -7830,11 +8058,11 @@
       <c r="J167">
         <v>2</v>
       </c>
-      <c r="O167" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R167" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>180</v>
       </c>
@@ -7865,11 +8093,11 @@
       <c r="J168">
         <v>2</v>
       </c>
-      <c r="O168" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R168" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>183</v>
       </c>
@@ -7900,11 +8128,11 @@
       <c r="J169">
         <v>2</v>
       </c>
-      <c r="O169" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R169" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>184</v>
       </c>
@@ -7935,14 +8163,14 @@
       <c r="J170">
         <v>1</v>
       </c>
-      <c r="N170" t="s">
+      <c r="O170" t="s">
         <v>185</v>
       </c>
-      <c r="O170" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R170" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>186</v>
       </c>
@@ -7973,11 +8201,11 @@
       <c r="J171">
         <v>2</v>
       </c>
-      <c r="O171" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R171" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>187</v>
       </c>
@@ -8017,11 +8245,20 @@
       <c r="M172" t="s">
         <v>190</v>
       </c>
-      <c r="O172" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N172" t="s">
+        <v>190</v>
+      </c>
+      <c r="P172" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>190</v>
+      </c>
+      <c r="R172" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>191</v>
       </c>
@@ -8052,11 +8289,11 @@
       <c r="J173">
         <v>1</v>
       </c>
-      <c r="O173" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R173" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>163</v>
       </c>
@@ -8087,14 +8324,14 @@
       <c r="J174">
         <v>2</v>
       </c>
-      <c r="N174" t="s">
+      <c r="O174" t="s">
         <v>192</v>
       </c>
-      <c r="O174" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R174" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>185</v>
       </c>
@@ -8125,11 +8362,11 @@
       <c r="J175">
         <v>1</v>
       </c>
-      <c r="O175" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R175" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>193</v>
       </c>
@@ -8160,11 +8397,11 @@
       <c r="J176">
         <v>2</v>
       </c>
-      <c r="O176" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R176" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>194</v>
       </c>
@@ -8195,11 +8432,11 @@
       <c r="J177">
         <v>1</v>
       </c>
-      <c r="O177" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R177" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>188</v>
       </c>
@@ -8230,11 +8467,11 @@
       <c r="J178">
         <v>1</v>
       </c>
-      <c r="O178" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R178" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>192</v>
       </c>
@@ -8265,11 +8502,11 @@
       <c r="J179">
         <v>2</v>
       </c>
-      <c r="O179" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R179" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -8300,11 +8537,11 @@
       <c r="J180">
         <v>1</v>
       </c>
-      <c r="O180" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R180" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>195</v>
       </c>
@@ -8335,11 +8572,11 @@
       <c r="J181">
         <v>1</v>
       </c>
-      <c r="O181" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R181" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>196</v>
       </c>
@@ -8370,11 +8607,11 @@
       <c r="J182">
         <v>3</v>
       </c>
-      <c r="O182" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R182" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>197</v>
       </c>
@@ -8405,11 +8642,11 @@
       <c r="J183">
         <v>2</v>
       </c>
-      <c r="O183" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R183" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>198</v>
       </c>
@@ -8440,14 +8677,14 @@
       <c r="J184">
         <v>1</v>
       </c>
-      <c r="N184" t="s">
+      <c r="O184" t="s">
         <v>199</v>
       </c>
-      <c r="O184" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R184" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>175</v>
       </c>
@@ -8478,11 +8715,11 @@
       <c r="J185">
         <v>1</v>
       </c>
-      <c r="O185" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R185" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>179</v>
       </c>
@@ -8513,11 +8750,11 @@
       <c r="J186">
         <v>3</v>
       </c>
-      <c r="O186" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R186" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>200</v>
       </c>
@@ -8548,11 +8785,11 @@
       <c r="J187">
         <v>2</v>
       </c>
-      <c r="O187" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R187" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>201</v>
       </c>
@@ -8583,14 +8820,14 @@
       <c r="J188">
         <v>1</v>
       </c>
-      <c r="N188" t="s">
+      <c r="O188" t="s">
         <v>202</v>
       </c>
-      <c r="O188" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R188" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -8621,11 +8858,11 @@
       <c r="J189">
         <v>2</v>
       </c>
-      <c r="O189" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R189" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>203</v>
       </c>
@@ -8656,11 +8893,11 @@
       <c r="J190">
         <v>1</v>
       </c>
-      <c r="O190" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R190" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>204</v>
       </c>
@@ -8691,11 +8928,11 @@
       <c r="J191">
         <v>1</v>
       </c>
-      <c r="O191" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R191" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>205</v>
       </c>
@@ -8735,11 +8972,20 @@
       <c r="M192" t="s">
         <v>207</v>
       </c>
-      <c r="O192" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N192" t="s">
+        <v>207</v>
+      </c>
+      <c r="P192" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>207</v>
+      </c>
+      <c r="R192" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>202</v>
       </c>
@@ -8770,11 +9016,11 @@
       <c r="J193">
         <v>1</v>
       </c>
-      <c r="O193" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R193" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>208</v>
       </c>
@@ -8805,11 +9051,11 @@
       <c r="J194">
         <v>1</v>
       </c>
-      <c r="O194" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R194" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>209</v>
       </c>
@@ -8840,11 +9086,11 @@
       <c r="J195">
         <v>2</v>
       </c>
-      <c r="O195" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R195" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>210</v>
       </c>
@@ -8875,11 +9121,11 @@
       <c r="J196">
         <v>2</v>
       </c>
-      <c r="O196" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R196" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>211</v>
       </c>
@@ -8910,11 +9156,11 @@
       <c r="J197">
         <v>3</v>
       </c>
-      <c r="O197" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R197" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>189</v>
       </c>
@@ -8945,11 +9191,11 @@
       <c r="J198">
         <v>2</v>
       </c>
-      <c r="O198" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R198" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>212</v>
       </c>
@@ -8980,11 +9226,11 @@
       <c r="J199">
         <v>1</v>
       </c>
-      <c r="O199" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R199" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -9024,11 +9270,20 @@
       <c r="M200" t="s">
         <v>215</v>
       </c>
-      <c r="O200" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N200" t="s">
+        <v>215</v>
+      </c>
+      <c r="P200" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>215</v>
+      </c>
+      <c r="R200" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>216</v>
       </c>
@@ -9059,11 +9314,11 @@
       <c r="J201">
         <v>2</v>
       </c>
-      <c r="O201" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R201" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>217</v>
       </c>
@@ -9094,11 +9349,11 @@
       <c r="J202">
         <v>1</v>
       </c>
-      <c r="O202" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R202" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>218</v>
       </c>
@@ -9129,11 +9384,11 @@
       <c r="J203">
         <v>3</v>
       </c>
-      <c r="O203" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R203" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>219</v>
       </c>
@@ -9164,11 +9419,11 @@
       <c r="J204">
         <v>1</v>
       </c>
-      <c r="O204" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R204" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>220</v>
       </c>
@@ -9199,11 +9454,11 @@
       <c r="J205">
         <v>2</v>
       </c>
-      <c r="O205" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R205" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -9234,11 +9489,11 @@
       <c r="J206">
         <v>3</v>
       </c>
-      <c r="O206" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R206" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>221</v>
       </c>
@@ -9269,11 +9524,11 @@
       <c r="J207">
         <v>2</v>
       </c>
-      <c r="O207" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R207" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -9304,11 +9559,11 @@
       <c r="J208">
         <v>1</v>
       </c>
-      <c r="O208" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R208" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>222</v>
       </c>
@@ -9339,11 +9594,11 @@
       <c r="J209">
         <v>1</v>
       </c>
-      <c r="O209" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R209" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>223</v>
       </c>
@@ -9374,11 +9629,11 @@
       <c r="J210">
         <v>2</v>
       </c>
-      <c r="O210" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R210" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>224</v>
       </c>
@@ -9416,13 +9671,22 @@
         <v>226</v>
       </c>
       <c r="N211" t="s">
+        <v>226</v>
+      </c>
+      <c r="O211" t="s">
         <v>227</v>
       </c>
-      <c r="O211" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P211" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>226</v>
+      </c>
+      <c r="R211" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>228</v>
       </c>
@@ -9459,11 +9723,20 @@
       <c r="M212" t="s">
         <v>229</v>
       </c>
-      <c r="O212" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N212" t="s">
+        <v>229</v>
+      </c>
+      <c r="P212" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>229</v>
+      </c>
+      <c r="R212" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>230</v>
       </c>
@@ -9494,11 +9767,11 @@
       <c r="J213">
         <v>2</v>
       </c>
-      <c r="O213" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R213" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>231</v>
       </c>
@@ -9529,11 +9802,11 @@
       <c r="J214">
         <v>2</v>
       </c>
-      <c r="O214" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R214" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>232</v>
       </c>
@@ -9564,14 +9837,14 @@
       <c r="J215">
         <v>3</v>
       </c>
-      <c r="N215" t="s">
+      <c r="O215" t="s">
         <v>229</v>
       </c>
-      <c r="O215" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R215" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>227</v>
       </c>
@@ -9602,11 +9875,11 @@
       <c r="J216">
         <v>2</v>
       </c>
-      <c r="O216" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R216" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>225</v>
       </c>
@@ -9637,11 +9910,11 @@
       <c r="J217">
         <v>3</v>
       </c>
-      <c r="O217" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R217" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>206</v>
       </c>
@@ -9672,11 +9945,11 @@
       <c r="J218">
         <v>1</v>
       </c>
-      <c r="O218" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R218" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>226</v>
       </c>
@@ -9707,11 +9980,11 @@
       <c r="J219">
         <v>2</v>
       </c>
-      <c r="O219" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R219" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>229</v>
       </c>
@@ -9742,11 +10015,11 @@
       <c r="J220">
         <v>1</v>
       </c>
-      <c r="O220" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R220" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>233</v>
       </c>
@@ -9777,11 +10050,11 @@
       <c r="J221">
         <v>2</v>
       </c>
-      <c r="O221" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R221" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>234</v>
       </c>
@@ -9812,11 +10085,11 @@
       <c r="J222">
         <v>1</v>
       </c>
-      <c r="O222" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R222" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>235</v>
       </c>
@@ -9847,11 +10120,11 @@
       <c r="J223">
         <v>1</v>
       </c>
-      <c r="O223" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R223" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>236</v>
       </c>
@@ -9888,11 +10161,20 @@
       <c r="M224" t="s">
         <v>238</v>
       </c>
-      <c r="O224" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N224" t="s">
+        <v>238</v>
+      </c>
+      <c r="P224" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>238</v>
+      </c>
+      <c r="R224" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>239</v>
       </c>
@@ -9923,14 +10205,14 @@
       <c r="J225">
         <v>2</v>
       </c>
-      <c r="N225" t="s">
+      <c r="O225" t="s">
         <v>237</v>
       </c>
-      <c r="O225" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R225" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>214</v>
       </c>
@@ -9961,11 +10243,11 @@
       <c r="J226">
         <v>1</v>
       </c>
-      <c r="O226" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R226" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>240</v>
       </c>
@@ -9996,11 +10278,11 @@
       <c r="J227">
         <v>1</v>
       </c>
-      <c r="O227" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R227" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>241</v>
       </c>
@@ -10031,11 +10313,11 @@
       <c r="J228">
         <v>1</v>
       </c>
-      <c r="O228" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R228" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>242</v>
       </c>
@@ -10066,14 +10348,14 @@
       <c r="J229">
         <v>2</v>
       </c>
-      <c r="N229" t="s">
+      <c r="O229" t="s">
         <v>243</v>
       </c>
-      <c r="O229" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R229" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>237</v>
       </c>
@@ -10104,11 +10386,11 @@
       <c r="J230">
         <v>1</v>
       </c>
-      <c r="O230" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R230" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>244</v>
       </c>
@@ -10139,11 +10421,11 @@
       <c r="J231">
         <v>1</v>
       </c>
-      <c r="O231" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R231" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>238</v>
       </c>
@@ -10174,11 +10456,11 @@
       <c r="J232">
         <v>1</v>
       </c>
-      <c r="O232" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R232" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>245</v>
       </c>
@@ -10209,11 +10491,11 @@
       <c r="J233">
         <v>2</v>
       </c>
-      <c r="O233" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R233" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>243</v>
       </c>
@@ -10244,14 +10526,15 @@
       <c r="J234">
         <v>2</v>
       </c>
-      <c r="O234" t="s">
-        <v>249</v>
+      <c r="R234" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N234" xr:uid="{041A12D7-D1F2-5E4A-959D-815F4F1F9005}"/>
+  <autoFilter ref="A1:O234" xr:uid="{041A12D7-D1F2-5E4A-959D-815F4F1F9005}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:N1048576" xr:uid="{836F0146-E07F-2A4C-BD11-FE221837FD18}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:Q1048576" xr:uid="{836F0146-E07F-2A4C-BD11-FE221837FD18}">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
